--- a/testAutomation_v1.0/test/Manual/C1App/AdminApp-Reports/AdminApp_Reports_tab_test_cases.xlsx
+++ b/testAutomation_v1.0/test/Manual/C1App/AdminApp-Reports/AdminApp_Reports_tab_test_cases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="297">
   <si>
     <t>S.No.</t>
   </si>
@@ -84,7 +84,7 @@
     <t>URL is /admin/admin/org_&lt;slug&gt;/reports. The heading reads "Reports (0)". A "Create report" button is present. The informational line reads "Reports are available to download for up to 60 days". The empty state reads "No new reports available" above "Your reports will appear here after you create them", with a second "Create report" button.</t>
   </si>
   <si>
-    <t>All copy captured verbatim live 2026-08-26. The (0) count is school-specific — on a school that already holds reports this case cannot show the empty state.</t>
+    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. All copy captured verbatim live 2026-08-26. The (0) count is school-specific — on a school that already holds reports this case cannot show the empty state.</t>
   </si>
   <si>
     <t/>
@@ -131,7 +131,7 @@
     <t>The app returns to /admin/admin/org_&lt;slug&gt;/reports, the Reports tab renders, and no new report has been created (the heading count is unchanged).</t>
   </si>
   <si>
-    <t>Distinct from the footer "Cancel" (TST_MRPT_TC_18) — both exit paths need covering.</t>
+    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Distinct from the footer "Cancel" (TST_MRPT_TC_18) — both exit paths need covering.</t>
   </si>
   <si>
     <t>TST_MRPT_TC_4</t>
@@ -422,7 +422,7 @@
     <t>[ASSUMED] Selection is capped at 1500 and the product surfaces the limit it states on screen ("You can include up to 1500 classes").</t>
   </si>
   <si>
-    <t>BLOCKED at design time. The cap text is captured verbatim live, but VED-NEH-KVU holds only 6 classes so the cap cannot be reached. UNBLOCK: a dedicated school seeded with &gt;1500 classes, or a product/API confirmation. Whether the cap blocks further ticks or raises a message is unknown.</t>
+    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. BLOCKED at design time. The cap text is captured verbatim live, but VED-NEH-KVU holds only 6 classes so the cap cannot be reached. UNBLOCK: a dedicated school seeded with &gt;1500 classes, or a product/API confirmation. Whether the cap blocks further ticks or raises a message is unknown.</t>
   </si>
   <si>
     <t>Blocked</t>
@@ -719,7 +719,7 @@
     <t>Dates before 1 January 2022 are not selectable; 1 January 2022 itself is selectable.</t>
   </si>
   <si>
-    <t>Verified live 2026-08-26 from the field attributes: the "From" input carries min="2021-12-31T18:30:00.000Z", i.e. 2022-01-01 in IST. Exactly the kind of field constraint admin-shared.md §A3 requires be read before writing boundary cases.</t>
+    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Verified live 2026-08-26 from the field attributes: the "From" input carries min="2021-12-31T18:30:00.000Z", i.e. 2022-01-01 in IST. Exactly the kind of field constraint admin-shared.md §A3 requires be read before writing boundary cases.</t>
   </si>
   <si>
     <t>TST_MRPT_TC_30</t>
@@ -739,7 +739,7 @@
     <t>All dates after today are disabled in both pickers; today is selectable in both.</t>
   </si>
   <si>
-    <t>Verified live 2026-08-26: both inputs carry max="2026-08-26T18:29:59.999Z" (end of the current day). Reports cover past activity only.</t>
+    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Verified live 2026-08-26: both inputs carry max="2026-08-26T18:29:59.999Z" (end of the current day). Reports cover past activity only.</t>
   </si>
   <si>
     <t>TST_MRPT_TC_31</t>
@@ -780,7 +780,7 @@
     <t>Neither field accepts typed input; both retain their picker-set values. Dates can be set only through the calendar pickers.</t>
   </si>
   <si>
-    <t>Verified live 2026-08-26: both "From" and "To" inputs are readOnly. This rules out the whole family of "type an invalid date" negative cases — the pickers are the only input path.</t>
+    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Verified live 2026-08-26: both "From" and "To" inputs are readOnly. This rules out the whole family of "type an invalid date" negative cases — the pickers are the only input path.</t>
   </si>
   <si>
     <t>TST_MRPT_TC_33</t>
@@ -801,7 +801,7 @@
     <t>For all three types the "Custom date range" radio remains DISABLED and "From the beginning" stays selected — no "From"/"To" fields can be produced.</t>
   </si>
   <si>
-    <t>Verified live 2026-08-26 across all seven types. Date range is supported by exactly four (Class summary, Class detailed data, Class daily data, Aggregated data), which matches the four named in scenario #12 — the scenario list is correct, and this case pins the negative half of it.</t>
+    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Verified live 2026-08-26 across all seven types. Date range is supported by exactly four (Class summary, Class detailed data, Class daily data, Aggregated data), which matches the four named in scenario #12 — the scenario list is correct, and this case pins the negative half of it.</t>
   </si>
   <si>
     <t>TST_MRPT_TC_34</t>
@@ -872,7 +872,7 @@
     <t>The checkbox is DISABLED and cannot be ticked.</t>
   </si>
   <si>
-    <t>Verified live 2026-08-26. Estimated CEFR level is the only one of the seven types supporting neither a custom date range nor custom grade settings — which is why it appears in neither scenario #12 nor #13.</t>
+    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Verified live 2026-08-26. Estimated CEFR level is the only one of the seven types supporting neither a custom date range nor custom grade settings — which is why it appears in neither scenario #12 nor #13.</t>
   </si>
   <si>
     <t>TST_MRPT_TC_37</t>
@@ -924,7 +924,7 @@
     <t>A dialog is shown headed "Sorry, something went wrong. The report you requested was not generated." offering "Try again" and "Back to Reports".</t>
   </si>
   <si>
-    <t>BLOCKED at design time. The copy above was captured verbatim from the PRE-RENDERED DOM on 2026-08-26 (admin-shared.md §A6 free-capture), so the expected result is verified even though the state was never reached. UNBLOCK: backend fault injection or a stubbed failure response. A second, separate failure surface exists on the Reports tab itself — see TST_MRPT_TC_39.</t>
+    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. BLOCKED at design time. The copy above was captured verbatim from the PRE-RENDERED DOM on 2026-08-26 (admin-shared.md §A6 free-capture), so the expected result is verified even though the state was never reached. UNBLOCK: backend fault injection or a stubbed failure response. A second, separate failure surface exists on the Reports tab itself — see TST_MRPT_TC_39.</t>
   </si>
   <si>
     <t>Blocked at design time — report generation failure cannot be forced on Thor.</t>
@@ -947,10 +947,88 @@
     <t>A modal headed "Report created with errors" states "&lt;N&gt; out of &lt;TOTAL&gt; classes were not included in your report due to the errors shown below" above a table with the columns "Class name", "Class key" and "Error message", and offers "Download report".</t>
   </si>
   <si>
-    <t>BLOCKED at design time. Copy captured from the pre-rendered DOM on the Reports tab 2026-08-26. Requires a multi-class report in which some classes fail — cannot be produced on demand. UNBLOCK: fault injection, or a class deliberately placed in a state that fails report generation.</t>
+    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. BLOCKED at design time. Copy captured from the pre-rendered DOM on the Reports tab 2026-08-26. Requires a multi-class report in which some classes fail — cannot be produced on demand. UNBLOCK: fault injection, or a class deliberately placed in a state that fails report generation.</t>
   </si>
   <si>
     <t>Blocked at design time — a partially-failing report cannot be produced on Thor.</t>
+  </si>
+  <si>
+    <t>TST_MRPT_TC_40</t>
+  </si>
+  <si>
+    <t>Verify the report class-selection filter narrows the list by class label</t>
+  </si>
+  <si>
+    <t>#3 - Verify filter</t>
+  </si>
+  <si>
+    <t>In the report creation flow at the class-selection step, on a school with at least one labelled class.</t>
+  </si>
+  <si>
+    <t>1. Click Create report to reach class selection. 2. Open Filter. 3. Record which filter groups the panel offers. 4. If class labels are offered, select one and Apply. 5. Read the resulting class list.</t>
+  </si>
+  <si>
+    <t>Label &lt;EXISTING_THOR_CLASS_LABEL&gt;.</t>
+  </si>
+  <si>
+    <t>The class list is narrowed to classes carrying the selected label, and a label combined with a status behaves as an AND. [ASSUMED] - and the premise itself is unconfirmed.</t>
+  </si>
+  <si>
+    <t>Added 2026-09-01 from the other team's TC_REP_003, which says "status/label filter". All five of our filter cases (TST_MRPT_TC_8-TC_12) are class-STATUS only, and TST_MRPT_TC_8 asserts the panel opens with five class statuses - with no mention of labels. GROUND FIRST: if the report-flow panel offers statuses only, their sheet is wrong and this becomes a correction rather than a new case. The label filter definitely exists on the Classes tab (TST_CLST_TC_4); whether the report flow reuses that panel is the open question. Read-only.</t>
+  </si>
+  <si>
+    <t>TST_MRPT_TC_41</t>
+  </si>
+  <si>
+    <t>Verify a generated report contains data that reconciles with the class it was run against</t>
+  </si>
+  <si>
+    <t>#6 - Verify Class summary report from beginning</t>
+  </si>
+  <si>
+    <t>A fixture class whose activity data is known and stable, with a report generated over it.</t>
+  </si>
+  <si>
+    <t>1. Record the fixture class's known activity - enrolled students and their completed activities/scores. 2. Generate a Class summary report "From the beginning" and download it. 3. Reconcile the file against the recorded data: one row per enrolled student, totals summing correctly. 4. Repeat for Aggregated data and confirm its figures sum/average the underlying class-level data.</t>
+  </si>
+  <si>
+    <t>Fixture class &lt;FROZEN_ACTIVITY_CLASS&gt; with known, unchanging activity.</t>
+  </si>
+  <si>
+    <t>The downloaded report reflects the class's actual data: every enrolled student is represented, totals and averages are arithmetically correct, and no activity outside the requested window appears. [ASSUMED]</t>
+  </si>
+  <si>
+    <t>Added 2026-09-01 - the most significant gap found in the whole comparison. Our seven generation cases (TST_MRPT_TC_21-TC_26, TC_37) all stop at "the report is created and listed for download"; every one of the other team's equivalents (TC_REP_006-TC_REP_012) asserts the numbers inside. A report that generates successfully with wrong content passes every case we currently hold. Written against Class summary and Aggregated data as the two highest-value types; extend to the rest once the fixture exists.</t>
+  </si>
+  <si>
+    <t>Blocked at design time (skill rule 4): reconciliation needs a class whose activity is seeded and frozen. 3 July Test School 1 is shared and its activity changes under other suites, so figures would not be reproducible. Unblock by provisioning a fixture class with known, stable activity data - this is the single most valuable fixture on the Reports backlog.</t>
+  </si>
+  <si>
+    <t>TST_MRPT_TC_42</t>
+  </si>
+  <si>
+    <t>Verify a custom grade exclusion is respected consistently across every report type that supports it</t>
+  </si>
+  <si>
+    <t>#13 - Verify reports with custom grade settings applied</t>
+  </si>
+  <si>
+    <t>A class whose grade settings exclude one component or category from the grade, with known activity on the excluded item.</t>
+  </si>
+  <si>
+    <t>1. Configure the class grade settings to exclude one component/category. 2. Generate each supported type with the custom grade option ticked: Class summary, Class detailed data, Class daily data, Aggregated data, Assignments summary, Assignments detailed data. 3. In each output, confirm the excluded item is absent and the totals recompute without it.</t>
+  </si>
+  <si>
+    <t>Class &lt;FROZEN_ACTIVITY_CLASS&gt; with one component excluded from the grade.</t>
+  </si>
+  <si>
+    <t>All six report types consistently omit the excluded component and recompute their totals/averages without it. [ASSUMED]</t>
+  </si>
+  <si>
+    <t>Added 2026-09-01 from the other team's TC_REP_014, which sweeps the exclusion across all six types. Our TST_MRPT_TC_35 proves the option takes effect on one report; consistency across types was untested - and inconsistency between report types is precisely the defect this guards against. Depends on the same fixture as TST_MRPT_TC_41.</t>
+  </si>
+  <si>
+    <t>Blocked at design time: depends on the seeded, frozen-activity fixture class described in TST_MRPT_TC_41. Unblock together.</t>
   </si>
 </sst>
 </file>
@@ -1342,7 +1420,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N40"/>
+  <dimension ref="A1:N43"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -3120,8 +3198,140 @@
         <v>270</v>
       </c>
     </row>
+    <row r="41" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="2">
+        <v>40</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="J41" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="K41" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="L41" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M41" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="N41" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="2">
+        <v>41</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="J42" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="K42" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="L42" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M42" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="N42" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="2">
+        <v>42</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="I43" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="J43" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="K43" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="L43" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M43" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="N43" s="2" t="s">
+        <v>296</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>